--- a/Datasheets/pcbuilder_import_data_20260902_gpu.xlsx
+++ b/Datasheets/pcbuilder_import_data_20260902_gpu.xlsx
@@ -1,15 +1,415 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="Gpus" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gpus" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
 </workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -36,12 +436,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>01934604-837d-478f-a480-784aca7c052a</t>
+          <t>e57308d7-f663-4e92-98ec-ed81dde721c1</t>
         </is>
       </c>
     </row>
@@ -53,12 +453,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>01934604-837d-478f-a480-784aca7c052a</t>
+          <t>e57308d7-f663-4e92-98ec-ed81dde721c1</t>
         </is>
       </c>
     </row>
@@ -70,12 +470,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>01934604-837d-478f-a480-784aca7c052a</t>
+          <t>e57308d7-f663-4e92-98ec-ed81dde721c1</t>
         </is>
       </c>
     </row>
@@ -87,12 +487,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>01934604-837d-478f-a480-784aca7c052a</t>
+          <t>e57308d7-f663-4e92-98ec-ed81dde721c1</t>
         </is>
       </c>
     </row>
@@ -104,12 +504,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>01934604-837d-478f-a480-784aca7c052a</t>
+          <t>e57308d7-f663-4e92-98ec-ed81dde721c1</t>
         </is>
       </c>
     </row>
@@ -121,12 +521,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>01934604-837d-478f-a480-784aca7c052a</t>
+          <t>e57308d7-f663-4e92-98ec-ed81dde721c1</t>
         </is>
       </c>
     </row>
@@ -138,12 +538,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>01934604-837d-478f-a480-784aca7c052a</t>
+          <t>e57308d7-f663-4e92-98ec-ed81dde721c1</t>
         </is>
       </c>
     </row>
@@ -155,12 +555,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>01934604-837d-478f-a480-784aca7c052a</t>
+          <t>e57308d7-f663-4e92-98ec-ed81dde721c1</t>
         </is>
       </c>
     </row>
@@ -172,12 +572,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>01934604-837d-478f-a480-784aca7c052a</t>
+          <t>e57308d7-f663-4e92-98ec-ed81dde721c1</t>
         </is>
       </c>
     </row>
@@ -189,12 +589,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>01934604-837d-478f-a480-784aca7c052a</t>
+          <t>e57308d7-f663-4e92-98ec-ed81dde721c1</t>
         </is>
       </c>
     </row>
@@ -206,12 +606,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>01934604-837d-478f-a480-784aca7c052a</t>
+          <t>e57308d7-f663-4e92-98ec-ed81dde721c1</t>
         </is>
       </c>
     </row>
@@ -223,12 +623,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>01934604-837d-478f-a480-784aca7c052a</t>
+          <t>e57308d7-f663-4e92-98ec-ed81dde721c1</t>
         </is>
       </c>
     </row>
@@ -240,12 +640,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>01934604-837d-478f-a480-784aca7c052a</t>
+          <t>e57308d7-f663-4e92-98ec-ed81dde721c1</t>
         </is>
       </c>
     </row>
@@ -257,12 +657,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2785d132-1537-4eae-b4ce-fe13f1fce9d2</t>
+          <t>10406586-1cf9-4521-9701-0139190b305f</t>
         </is>
       </c>
     </row>
@@ -274,12 +674,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2785d132-1537-4eae-b4ce-fe13f1fce9d2</t>
+          <t>10406586-1cf9-4521-9701-0139190b305f</t>
         </is>
       </c>
     </row>
@@ -291,12 +691,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2785d132-1537-4eae-b4ce-fe13f1fce9d2</t>
+          <t>10406586-1cf9-4521-9701-0139190b305f</t>
         </is>
       </c>
     </row>
@@ -308,12 +708,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2785d132-1537-4eae-b4ce-fe13f1fce9d2</t>
+          <t>10406586-1cf9-4521-9701-0139190b305f</t>
         </is>
       </c>
     </row>
@@ -325,12 +725,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2785d132-1537-4eae-b4ce-fe13f1fce9d2</t>
+          <t>10406586-1cf9-4521-9701-0139190b305f</t>
         </is>
       </c>
     </row>
@@ -342,12 +742,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2785d132-1537-4eae-b4ce-fe13f1fce9d2</t>
+          <t>10406586-1cf9-4521-9701-0139190b305f</t>
         </is>
       </c>
     </row>
@@ -359,12 +759,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2785d132-1537-4eae-b4ce-fe13f1fce9d2</t>
+          <t>10406586-1cf9-4521-9701-0139190b305f</t>
         </is>
       </c>
     </row>
@@ -376,12 +776,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>5652e237-1353-43aa-8c9c-ab86f4f1128f</t>
+          <t>31c2ee19-688b-4bcd-9f13-7458d3913009</t>
         </is>
       </c>
     </row>
@@ -393,12 +793,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5652e237-1353-43aa-8c9c-ab86f4f1128f</t>
+          <t>31c2ee19-688b-4bcd-9f13-7458d3913009</t>
         </is>
       </c>
     </row>
@@ -410,12 +810,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>5652e237-1353-43aa-8c9c-ab86f4f1128f</t>
+          <t>31c2ee19-688b-4bcd-9f13-7458d3913009</t>
         </is>
       </c>
     </row>
@@ -427,12 +827,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5652e237-1353-43aa-8c9c-ab86f4f1128f</t>
+          <t>31c2ee19-688b-4bcd-9f13-7458d3913009</t>
         </is>
       </c>
     </row>
@@ -444,12 +844,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5652e237-1353-43aa-8c9c-ab86f4f1128f</t>
+          <t>31c2ee19-688b-4bcd-9f13-7458d3913009</t>
         </is>
       </c>
     </row>
@@ -461,12 +861,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>5652e237-1353-43aa-8c9c-ab86f4f1128f</t>
+          <t>31c2ee19-688b-4bcd-9f13-7458d3913009</t>
         </is>
       </c>
     </row>
@@ -478,12 +878,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>5652e237-1353-43aa-8c9c-ab86f4f1128f</t>
+          <t>31c2ee19-688b-4bcd-9f13-7458d3913009</t>
         </is>
       </c>
     </row>
@@ -495,12 +895,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
+          <t>dd191e11-e1e5-4b65-89c0-a28a4d8f6ce1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>5652e237-1353-43aa-8c9c-ab86f4f1128f</t>
+          <t>31c2ee19-688b-4bcd-9f13-7458d3913009</t>
         </is>
       </c>
     </row>
@@ -512,12 +912,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
+          <t>7fd65649-5c4a-49b6-bb70-e34d4f4a8908</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>42172481-060f-4de2-baca-85963548abc1</t>
+          <t>3cde3b16-b535-4b0d-b90e-e5571883c8a4</t>
         </is>
       </c>
     </row>
@@ -529,12 +929,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
+          <t>7fd65649-5c4a-49b6-bb70-e34d4f4a8908</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>42172481-060f-4de2-baca-85963548abc1</t>
+          <t>3cde3b16-b535-4b0d-b90e-e5571883c8a4</t>
         </is>
       </c>
     </row>
@@ -546,12 +946,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
+          <t>7fd65649-5c4a-49b6-bb70-e34d4f4a8908</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>42172481-060f-4de2-baca-85963548abc1</t>
+          <t>3cde3b16-b535-4b0d-b90e-e5571883c8a4</t>
         </is>
       </c>
     </row>
@@ -563,12 +963,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
+          <t>7fd65649-5c4a-49b6-bb70-e34d4f4a8908</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>42172481-060f-4de2-baca-85963548abc1</t>
+          <t>3cde3b16-b535-4b0d-b90e-e5571883c8a4</t>
         </is>
       </c>
     </row>
@@ -580,12 +980,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
+          <t>7fd65649-5c4a-49b6-bb70-e34d4f4a8908</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>4617fa05-8d76-4242-947a-f963c3dc082a</t>
+          <t>7129a8d9-94e4-4a91-bbcd-71a916bca00d</t>
         </is>
       </c>
     </row>
@@ -597,12 +997,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
+          <t>7fd65649-5c4a-49b6-bb70-e34d4f4a8908</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>4617fa05-8d76-4242-947a-f963c3dc082a</t>
+          <t>7129a8d9-94e4-4a91-bbcd-71a916bca00d</t>
         </is>
       </c>
     </row>
@@ -614,12 +1014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>78c6a9a7-8e5c-4e4e-9abc-a75770c93f0f</t>
+          <t>42c7ec51-d275-41ec-98b3-12cb813ff462</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>22cf0d81-150d-4608-bf5c-3ec4f7d05bed</t>
+          <t>6dd158d8-d584-4747-8cfd-13110b528aa2</t>
         </is>
       </c>
     </row>
@@ -631,12 +1031,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>78c6a9a7-8e5c-4e4e-9abc-a75770c93f0f</t>
+          <t>42c7ec51-d275-41ec-98b3-12cb813ff462</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>22cf0d81-150d-4608-bf5c-3ec4f7d05bed</t>
+          <t>6dd158d8-d584-4747-8cfd-13110b528aa2</t>
         </is>
       </c>
     </row>
@@ -648,12 +1048,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>78c6a9a7-8e5c-4e4e-9abc-a75770c93f0f</t>
+          <t>42c7ec51-d275-41ec-98b3-12cb813ff462</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>22cf0d81-150d-4608-bf5c-3ec4f7d05bed</t>
+          <t>6dd158d8-d584-4747-8cfd-13110b528aa2</t>
         </is>
       </c>
     </row>
@@ -665,12 +1065,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>78c6a9a7-8e5c-4e4e-9abc-a75770c93f0f</t>
+          <t>42c7ec51-d275-41ec-98b3-12cb813ff462</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>22cf0d81-150d-4608-bf5c-3ec4f7d05bed</t>
+          <t>6dd158d8-d584-4747-8cfd-13110b528aa2</t>
         </is>
       </c>
     </row>
@@ -682,12 +1082,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>78c6a9a7-8e5c-4e4e-9abc-a75770c93f0f</t>
+          <t>42c7ec51-d275-41ec-98b3-12cb813ff462</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>22cf0d81-150d-4608-bf5c-3ec4f7d05bed</t>
+          <t>6dd158d8-d584-4747-8cfd-13110b528aa2</t>
         </is>
       </c>
     </row>
@@ -699,12 +1099,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>78c6a9a7-8e5c-4e4e-9abc-a75770c93f0f</t>
+          <t>42c7ec51-d275-41ec-98b3-12cb813ff462</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>22cf0d81-150d-4608-bf5c-3ec4f7d05bed</t>
+          <t>6dd158d8-d584-4747-8cfd-13110b528aa2</t>
         </is>
       </c>
     </row>
@@ -716,12 +1116,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>78c6a9a7-8e5c-4e4e-9abc-a75770c93f0f</t>
+          <t>42c7ec51-d275-41ec-98b3-12cb813ff462</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>22cf0d81-150d-4608-bf5c-3ec4f7d05bed</t>
+          <t>6dd158d8-d584-4747-8cfd-13110b528aa2</t>
         </is>
       </c>
     </row>
@@ -733,12 +1133,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>78c6a9a7-8e5c-4e4e-9abc-a75770c93f0f</t>
+          <t>42c7ec51-d275-41ec-98b3-12cb813ff462</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>22cf0d81-150d-4608-bf5c-3ec4f7d05bed</t>
+          <t>6dd158d8-d584-4747-8cfd-13110b528aa2</t>
         </is>
       </c>
     </row>
@@ -750,12 +1150,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>78c6a9a7-8e5c-4e4e-9abc-a75770c93f0f</t>
+          <t>42c7ec51-d275-41ec-98b3-12cb813ff462</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>22cf0d81-150d-4608-bf5c-3ec4f7d05bed</t>
+          <t>6dd158d8-d584-4747-8cfd-13110b528aa2</t>
         </is>
       </c>
     </row>
@@ -767,12 +1167,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>78c6a9a7-8e5c-4e4e-9abc-a75770c93f0f</t>
+          <t>42c7ec51-d275-41ec-98b3-12cb813ff462</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>22cf0d81-150d-4608-bf5c-3ec4f7d05bed</t>
+          <t>6dd158d8-d584-4747-8cfd-13110b528aa2</t>
         </is>
       </c>
     </row>
@@ -784,12 +1184,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>78c6a9a7-8e5c-4e4e-9abc-a75770c93f0f</t>
+          <t>42c7ec51-d275-41ec-98b3-12cb813ff462</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>5dfb9e7e-4442-409e-986c-53de3ab586b8</t>
+          <t>59573843-4672-4a9e-91d3-473b6fcd756d</t>
         </is>
       </c>
     </row>
@@ -801,12 +1201,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>78c6a9a7-8e5c-4e4e-9abc-a75770c93f0f</t>
+          <t>42c7ec51-d275-41ec-98b3-12cb813ff462</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>5dfb9e7e-4442-409e-986c-53de3ab586b8</t>
+          <t>59573843-4672-4a9e-91d3-473b6fcd756d</t>
         </is>
       </c>
     </row>
@@ -818,12 +1218,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>78c6a9a7-8e5c-4e4e-9abc-a75770c93f0f</t>
+          <t>42c7ec51-d275-41ec-98b3-12cb813ff462</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>5dfb9e7e-4442-409e-986c-53de3ab586b8</t>
+          <t>59573843-4672-4a9e-91d3-473b6fcd756d</t>
         </is>
       </c>
     </row>
@@ -835,12 +1235,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>78c6a9a7-8e5c-4e4e-9abc-a75770c93f0f</t>
+          <t>42c7ec51-d275-41ec-98b3-12cb813ff462</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>5dfb9e7e-4442-409e-986c-53de3ab586b8</t>
+          <t>59573843-4672-4a9e-91d3-473b6fcd756d</t>
         </is>
       </c>
     </row>
@@ -852,12 +1252,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>78c6a9a7-8e5c-4e4e-9abc-a75770c93f0f</t>
+          <t>42c7ec51-d275-41ec-98b3-12cb813ff462</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>5dfb9e7e-4442-409e-986c-53de3ab586b8</t>
+          <t>59573843-4672-4a9e-91d3-473b6fcd756d</t>
         </is>
       </c>
     </row>
@@ -869,12 +1269,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>78c6a9a7-8e5c-4e4e-9abc-a75770c93f0f</t>
+          <t>42c7ec51-d275-41ec-98b3-12cb813ff462</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>5dfb9e7e-4442-409e-986c-53de3ab586b8</t>
+          <t>59573843-4672-4a9e-91d3-473b6fcd756d</t>
         </is>
       </c>
     </row>
@@ -886,12 +1286,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>78c6a9a7-8e5c-4e4e-9abc-a75770c93f0f</t>
+          <t>42c7ec51-d275-41ec-98b3-12cb813ff462</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>5dfb9e7e-4442-409e-986c-53de3ab586b8</t>
+          <t>59573843-4672-4a9e-91d3-473b6fcd756d</t>
         </is>
       </c>
     </row>
@@ -903,12 +1303,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>78c6a9a7-8e5c-4e4e-9abc-a75770c93f0f</t>
+          <t>42c7ec51-d275-41ec-98b3-12cb813ff462</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>5dfb9e7e-4442-409e-986c-53de3ab586b8</t>
+          <t>59573843-4672-4a9e-91d3-473b6fcd756d</t>
         </is>
       </c>
     </row>
@@ -920,12 +1320,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>78c6a9a7-8e5c-4e4e-9abc-a75770c93f0f</t>
+          <t>42c7ec51-d275-41ec-98b3-12cb813ff462</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>5dfb9e7e-4442-409e-986c-53de3ab586b8</t>
+          <t>59573843-4672-4a9e-91d3-473b6fcd756d</t>
         </is>
       </c>
     </row>
@@ -937,12 +1337,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>78c6a9a7-8e5c-4e4e-9abc-a75770c93f0f</t>
+          <t>42c7ec51-d275-41ec-98b3-12cb813ff462</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>79035fdc-de2b-4d66-b3d7-caba283783d5</t>
+          <t>6f3a7f00-6677-4941-a279-4ed51fa2bb00</t>
         </is>
       </c>
     </row>
@@ -954,12 +1354,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>78c6a9a7-8e5c-4e4e-9abc-a75770c93f0f</t>
+          <t>42c7ec51-d275-41ec-98b3-12cb813ff462</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>79035fdc-de2b-4d66-b3d7-caba283783d5</t>
+          <t>6f3a7f00-6677-4941-a279-4ed51fa2bb00</t>
         </is>
       </c>
     </row>
@@ -971,12 +1371,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>78c6a9a7-8e5c-4e4e-9abc-a75770c93f0f</t>
+          <t>42c7ec51-d275-41ec-98b3-12cb813ff462</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>79035fdc-de2b-4d66-b3d7-caba283783d5</t>
+          <t>6f3a7f00-6677-4941-a279-4ed51fa2bb00</t>
         </is>
       </c>
     </row>
@@ -988,12 +1388,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>78c6a9a7-8e5c-4e4e-9abc-a75770c93f0f</t>
+          <t>42c7ec51-d275-41ec-98b3-12cb813ff462</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>79035fdc-de2b-4d66-b3d7-caba283783d5</t>
+          <t>6f3a7f00-6677-4941-a279-4ed51fa2bb00</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1405,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>78c6a9a7-8e5c-4e4e-9abc-a75770c93f0f</t>
+          <t>42c7ec51-d275-41ec-98b3-12cb813ff462</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>79035fdc-de2b-4d66-b3d7-caba283783d5</t>
+          <t>6f3a7f00-6677-4941-a279-4ed51fa2bb00</t>
         </is>
       </c>
     </row>
@@ -1022,15 +1422,16 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>78c6a9a7-8e5c-4e4e-9abc-a75770c93f0f</t>
+          <t>42c7ec51-d275-41ec-98b3-12cb813ff462</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>79035fdc-de2b-4d66-b3d7-caba283783d5</t>
+          <t>6f3a7f00-6677-4941-a279-4ed51fa2bb00</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>